--- a/帝国时代2决定版 文明联盟 炮塔流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 炮塔流最优研究顺序 By RemonBo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开局3免费位" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续2000金顺序" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甲类·炮塔本体强化" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·石料与前置" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·减费用与资源效率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="与炮塔无关·可跳过" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主选文明推荐" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全62文明总名次" sheetId="7" state="visible" r:id="rId7"/>
@@ -20,10 +20,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·炮塔本体强化'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·炮塔本体强化'!$A$1:$E$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·炮塔本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·石料与前置'!$A$1:$E$21</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·石料与前置'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$23</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与炮塔无关·可跳过'!$A$1:$D$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与炮塔无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$19</definedName>
@@ -87,11 +87,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFE9CC"/>
       </patternFill>
     </fill>
@@ -103,6 +98,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EAF1FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -803,57 +803,57 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）；石矿工速度 +20%</t>
+          <t>长城：炮塔生命 +30%；科技费用 -5/10/15%</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>帝王时代 + 化学</t>
+          <t>帝王时代</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>白拿炮塔科技（800食/400木）与塔升级链，石料供给也一并解决——但「含炮塔升级」是原文括号的读法，需实测确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+          <t>【阶段1·本体强化】官方原文唯一把「炮塔」与「瞭望箭塔系」并列写出来的加成，炮塔生命 +30%；科技折价顺带压全表研究成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="66" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>城堡时代可用化学/火枪手；采矿场科技免费；铁匠铺/大学木材费用-100</t>
+          <t>火绳枪：炮塔对移动目标的准确度提高；科技研究速度 +25%（团队）</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>城堡时代即可点</t>
+          <t>帝王时代（城堡研究）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>比所有人早一个时代拿到「化学」这个唯一前置，到帝王时炮塔科技可以立刻点；铁匠铺/大学木材 -100 也压低升级支出</t>
+          <t>【阶段1·本体强化】官方帮助文本直接写「您城堡中的火绳枪科技提升了火药单位和炮塔对移动中目标的准确度」——全表唯一一条点名炮塔的命中加成，正好补炮塔「打不中快速单位」这个最大短板；科技研究 +25% 还能加速炮塔科技与整条大学升级链</t>
         </is>
       </c>
     </row>
@@ -863,57 +863,57 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>长城：炮塔生命 +30%；科技费用 -5/10/15%</t>
+          <t>塔驻扎容量 +5；近射孔、草药免费</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>帝王时代</t>
+          <t>封建起</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>官方原文唯一把「炮塔」与「瞭望箭塔系」并列写出来的加成，炮塔生命 +30%；科技折价顺带压全表研究成本</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="51" customHeight="1">
+          <t>【阶段1·本体强化】驻军 5→10，被拆时更难清空；近射孔免费消除最小射程，塔贴脸也能打</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>火绳枪：炮塔对移动目标的准确度提高；科技研究速度 +25%（团队）</t>
+          <t>斯万箭塔：防御工事攻击力 +2；建筑修理费用 -25%（团队）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>帝王时代（城堡研究）</t>
+          <t>城堡起</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>官方帮助文本直接写「您城堡中的火绳枪科技提升了火药单位和炮塔对移动中目标的准确度」——全表唯一一条点名炮塔的命中加成，正好补炮塔「打不中快速单位」这个最大短板；科技研究 +25% 还能加速炮塔科技与整条大学升级链</t>
+          <t>【阶段1·本体强化】防御工事含炮塔，但炮塔基数 120，+2 几乎无感；真正的价值是修理费 -25%</t>
         </is>
       </c>
     </row>
@@ -923,57 +923,57 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>初始石料 +100；防御工事建造速度 +50%</t>
+          <t>攻城和防御工事升级木材 -75%、研究 +100%；加固堡垒：防御工事每分钟回 500 生命</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>全局</t>
+          <t>全局 / 帝王</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>开局石料直接翻倍，且炮塔属防御工事，建造再快 50%——立塔速度和石料两处都省</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
+          <t>【阶段1·本体强化】炮塔的整条升级链（含大学防御工事科技）变便宜、研究快一倍，外加守塔时每分回 500 血</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>建筑的石料费用 -15%</t>
+          <t>箭毒：步弓手与防御工事可造成中毒伤害；塔楼和城堡提供的人口空间 +10（团队）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>全局</t>
+          <t>城堡起</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>炮塔石料 125 → 约 106，且同时压城堡、TC、城墙的石料，长局累积最明显</t>
+          <t>【阶段1·本体强化】防御工事含炮塔，但中毒是否作用于炮弹未验证；人口 +10 是确定的实用项</t>
         </is>
       </c>
     </row>
@@ -983,77 +983,77 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>攻城和防御工事升级木材 -75%、研究 +100%；加固堡垒：防御工事每分钟回 500 生命</t>
+          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）；石矿工速度 +20%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>全局 / 帝王</t>
+          <t>帝王时代 + 化学</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>炮塔的整条升级链（含大学防御工事科技）变便宜、研究快一倍，外加守塔时每分回 500 血</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
+          <t>【阶段2·减费用】白拿炮塔科技（800食/400木）与塔升级链，石料供给也一并解决——但「含炮塔升级」是原文括号的读法，需实测确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>建筑工速度 +30%；铁匠铺升级不耗金</t>
+          <t>城堡时代可用化学/火枪手；采矿场科技免费；铁匠铺/大学木材费用-100</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>全局</t>
+          <t>城堡时代即可点</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>炮塔的攻击与射程升级在铁匠铺，免金等于白拿；建筑工 +30% 让立塔更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
+          <t>【阶段2·减费用】比所有人早一个时代拿到「化学」这个唯一前置，到帝王时炮塔科技可以立刻点；铁匠铺/大学木材 -100 也压低升级支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>村民收集/建造/修理速度 +5%</t>
+          <t>建筑的石料费用 -15%</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>建造与修理同吃，长期守塔最省农民</t>
+          <t>【阶段2·减费用】炮塔石料 125 → 约 106，且同时压城堡、TC、城墙的石料，长局累积最明显</t>
         </is>
       </c>
     </row>
@@ -1073,27 +1073,27 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>石矿工产石料 + 黄金</t>
+          <t>TC 石料费用 -50%；城堡时代可建营垒</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>全局</t>
+          <t>全局 / 城堡</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>石料是第一瓶颈，这条直接把石料转化成黄金，长局石料不断档</t>
+          <t>【阶段2·减费用】石料折扣作用在 TC 与营垒，不是炮塔本体</t>
         </is>
       </c>
     </row>
@@ -1103,27 +1103,27 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>塔驻扎容量 +5；近射孔、草药免费</t>
+          <t>城墙费用 -50%（团队）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>封建起</t>
+          <t>全局</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>驻军 5→10，被拆时更难清空；近射孔免费消除最小射程，塔贴脸也能打</t>
+          <t>【阶段2·减费用】炮塔要站在墙上才安全，墙体便宜一半等于塔阵整体变便宜</t>
         </is>
       </c>
     </row>
@@ -1133,47 +1133,47 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>斯万箭塔：防御工事攻击力 +2；建筑修理费用 -25%（团队）</t>
+          <t>建筑工速度 +30%；铁匠铺升级不耗金</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>城堡起</t>
+          <t>全局</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>防御工事含炮塔，但炮塔基数 120，+2 几乎无感；真正的价值是修理费 -25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
+          <t>【阶段2·减费用】炮塔的攻击与射程升级在铁匠铺，免金等于白拿；建筑工 +30% 让立塔更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>城墙费用 -50%（团队）</t>
+          <t>初始石料 +100；防御工事建造速度 +50%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>炮塔要站在墙上才安全，墙体便宜一半等于塔阵整体变便宜</t>
+          <t>【阶段2·减费用】开局石料直接翻倍，且炮塔属防御工事，建造再快 50%——立塔速度和石料两处都省</t>
         </is>
       </c>
     </row>
@@ -1193,27 +1193,27 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>箭毒：步弓手与防御工事可造成中毒伤害；塔楼和城堡提供的人口空间 +10（团队）</t>
+          <t>石矿工产石料 + 黄金</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>城堡起</t>
+          <t>全局</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>防御工事含炮塔，但中毒是否作用于炮弹未验证；人口 +10 是确定的实用项</t>
+          <t>【阶段3·资源效率】石料是第一瓶颈，这条直接把石料转化成黄金，长局石料不断档</t>
         </is>
       </c>
     </row>
@@ -1223,27 +1223,27 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>TC 石料费用 -50%；城堡时代可建营垒</t>
+          <t>村民收集/建造/修理速度 +5%</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>全局 / 城堡</t>
+          <t>全局</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>石料折扣作用在 TC 与营垒，不是炮塔本体</t>
+          <t>【阶段3·资源效率】建造与修理同吃，长期守塔最省农民</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
           <t>埃塞俄比亚</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>哨站不等于炮塔，只是免费视野与省石料，属间接</t>
+          <t>【阶段3·资源效率】哨站不等于炮塔，只是免费视野与省石料，属间接</t>
         </is>
       </c>
     </row>
@@ -1286,9 +1286,9 @@
           <t>柏柏尔</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>作用在城堡，不是炮塔</t>
+          <t>【阶段4·其他相关】作用在城堡，不是炮塔</t>
         </is>
       </c>
     </row>
@@ -1316,9 +1316,9 @@
           <t>波斯</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>「堡垒」是城堡科技，作用对象是城堡</t>
+          <t>【阶段4·其他相关】「堡垒」是城堡科技，作用对象是城堡</t>
         </is>
       </c>
     </row>
@@ -1346,9 +1346,9 @@
           <t>不列颠</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>写的是「瞭望箭塔系」，与炮塔是两个不同单位线</t>
+          <t>【阶段4·其他相关】写的是「瞭望箭塔系」，与炮塔是两个不同单位线</t>
         </is>
       </c>
     </row>
@@ -1376,9 +1376,9 @@
           <t>凯尔特</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>「箭塔」是弓箭塔，炮塔不吃</t>
+          <t>【阶段4·其他相关】「箭塔」是弓箭塔，炮塔不吃</t>
         </is>
       </c>
     </row>
@@ -1406,9 +1406,9 @@
           <t>马里</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>作用对象是城镇中心</t>
+          <t>【阶段4·其他相关】作用对象是城镇中心</t>
         </is>
       </c>
     </row>
@@ -1436,9 +1436,9 @@
           <t>日本</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>炮塔发射的是炮弹，没有「箭矢」可加</t>
+          <t>【阶段4·其他相关】炮塔发射的是炮弹，没有「箭矢」可加</t>
         </is>
       </c>
     </row>
@@ -1466,9 +1466,9 @@
           <t>斯拉夫</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>官方原文写的是「瞭望塔系」，不含炮塔</t>
+          <t>【阶段4·其他相关】官方原文写的是「瞭望塔系」，不含炮塔</t>
         </is>
       </c>
     </row>
@@ -1496,9 +1496,9 @@
           <t>马其顿人</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>作用对象是哨站</t>
+          <t>【阶段4·其他相关】作用对象是哨站</t>
         </is>
       </c>
     </row>
@@ -1526,9 +1526,9 @@
           <t>普鲁人</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>「堡垒」是古典模式的 Fort 建筑，与炮塔无关</t>
+          <t>【阶段4·其他相关】「堡垒」是古典模式的 Fort 建筑，与炮塔无关</t>
         </is>
       </c>
     </row>
@@ -1556,9 +1556,9 @@
           <t>色雷斯人</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>是经济光环与存放点，不加炮塔战力</t>
+          <t>【阶段4·其他相关】是经济光环与存放点，不加炮塔战力</t>
         </is>
       </c>
     </row>
@@ -1586,9 +1586,9 @@
           <t>斯巴达</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>「堡垒」是古典模式建筑，仅产金</t>
+          <t>【阶段4·其他相关】「堡垒」是古典模式建筑，仅产金</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1658,7 +1658,7 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1685,7 +1685,7 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1712,7 +1712,7 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1739,7 +1739,7 @@
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1766,7 +1766,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1793,196 +1793,142 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
+          <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>炮塔属防御工事；但基数 120，+2 无感</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>条顿</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>塔驻扎容量+5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>原文括号即指炮塔升级，待实测确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>炮塔驻扎 5 → 10，塔更耐拆</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>火绳枪（火药单位攻击移动目标准确度更高）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>炮塔属防御工事；但基数 120，+2 无感</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>官方明写：提升火药单位与炮塔对移动目标的准确度——炮塔唯一的专属命中加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>箭毒（步弓手/防御工事造成中毒伤害）</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>防御工事含炮塔，是否作用于炮弹待实测</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>条顿</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>塔驻扎容量+5</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>近射孔/草药免费</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>炮塔驻扎 5 → 10，塔更耐拆</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>火绳枪（火药单位攻击移动目标准确度更高）</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>官方明写：提升火药单位与炮塔对移动目标的准确度——炮塔唯一的专属命中加成</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>箭毒（步弓手/防御工事造成中毒伤害）</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>防御工事含炮塔，是否作用于炮弹待实测</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>防御工事建造+50%，TC建造+100%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>炮塔属防御工事</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>条顿</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>近射孔/草药免费</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
           <t>近射孔消除防御工事最小射程</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1994,7 +1940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2031,548 +1977,602 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>原文括号即指炮塔升级，待实测确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>防御工事建造+50%，TC建造+100%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>炮塔属防御工事</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>土耳其</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>化学免费，火药技术成本-50%</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>省掉 300食/200金 + 100 秒前置；炮塔科技半价</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>波希米亚</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>城堡时代可用化学/火枪手</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>前置提前整整一个时代</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>高丽</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>石矿工速度+20%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>石料是第一瓶颈</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>拜占庭</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>升帝王费用-33%</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>全表唯一加速抵达帝王时代</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>拜占庭</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>建筑黑暗/封建/城堡/帝王生命+10/20/30/40%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>炮塔也是建筑，帝王 +40%</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>西西里</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>初始石料+100</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>开局就接近一座炮塔的石料</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>印加</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>建筑石料-15%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>炮塔 125 石 → 约 106 石</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>女真</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>攻城/防御工事升级木材-75%，研究+100%</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>炮塔升级链整体变便宜变快</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>西班牙</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>建筑工速度+30%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>炮塔立得更快</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>西班牙</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>铁匠铺升级不耗金</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>炮塔射程/攻击升级在铁匠铺</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>罗马</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>村民收集/建造/修理速度+5%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>建造与修理都在内</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>波兰</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>石矿工产石料+黄金</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>石料供给</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>格鲁吉亚</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>建筑修理费用 -25%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>守塔阶段省钱（团队）</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>撒克逊人</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>修理工的工作速度 +25%</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>守塔阶段更快补血（团队）</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>玛雅</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>城墙费用 -50%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>护塔墙体便宜一半（团队）</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>图皮</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>塔楼和城堡提供的人口空间 +10</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>塔阵省房屋（团队）</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>条顿</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>农田费用-40%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>纯经济换节奏</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>保加利亚</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>TC石料费用-50%</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>省的是 TC 不是炮塔</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>埃塞俄比亚</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>哨站视野 +3 且不消耗石料</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>哨站 ≠ 炮塔（团队）</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>西西里</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>黑暗可建城楼（替瞭望塔系）</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>城楼属瞭望塔系，非炮塔</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E21"/>
+  <autoFilter ref="A1:E23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3884,7 +3884,7 @@
           <t>土耳其</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>一个按钮同时解决「前置 + 成本 + 射程」三件事，全表最高杠杆；射程 8→10 后炮塔能压住除巨型投石机外的一切</t>
+          <t>【阶段1·本体强化】一个按钮同时解决「前置 + 成本 + 射程」三件事，全表最高杠杆；射程 8→10 后炮塔能压住除巨型投石机外的一切</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
           <t>拜占庭</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>既加炮塔本体生命，又是全表唯一加速抵达帝王时代的一条；再加爆炸范围，炮塔的「血厚、到得早、打得广」一次齐</t>
+          <t>【阶段1·本体强化】既加炮塔本体生命，又是全表唯一加速抵达帝王时代的一条；再加爆炸范围，炮塔的「血厚、到得早、打得广」一次齐</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
           <t>撒克逊人</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>dat 里这条加成是对 unit class 52（塔类）**通配**加值，而炮塔 236 的 class 正是 52——所以确实命中炮塔。注意 mod 把它从官方的 +1 放大成了 +5：炮塔的 TOTAL_MISSILES 基础值是 0（靠引擎保底射 1 发），官方 +1 属于 0→1 空转，而 +5 会真正变成多发炮弹。**前提是底座文明能造炮塔**（撒克逊自己造不了，只有结盟买到这个按钮的文明才吃得到）；附带的修理 +25% 还能加快补血。</t>
+          <t>【阶段1·本体强化】dat 里这条加成是对 unit class 52（塔类）**通配**加值，而炮塔 236 的 class 正是 52——所以确实命中炮塔。注意 mod 把它从官方的 +1 放大成了 +5：炮塔的 TOTAL_MISSILES 基础值是 0（靠引擎保底射 1 发），官方 +1 属于 0→1 空转，而 +5 会真正变成多发炮弹。**前提是底座文明能造炮塔**（撒克逊自己造不了，只有结盟买到这个按钮的文明才吃得到）；附带的修理 +25% 还能加快补血。</t>
         </is>
       </c>
     </row>
@@ -3971,12 +3971,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -3986,27 +3986,27 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）；石矿工速度 +20%</t>
+          <t>长城：炮塔生命 +30%；科技费用 -5/10/15%</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>白拿炮塔科技（800食/400木）与塔升级链，石料供给也一并解决——但「含炮塔升级」是原文括号的读法，需实测确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+          <t>【阶段1·本体强化】官方原文唯一把「炮塔」与「瞭望箭塔系」并列写出来的加成，炮塔生命 +30%；科技折价顺带压全表研究成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>城堡时代可用化学/火枪手；采矿场科技免费；铁匠铺/大学木材费用-100</t>
+          <t>火绳枪：炮塔对移动目标的准确度提高；科技研究速度 +25%（团队）</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>比所有人早一个时代拿到「化学」这个唯一前置，到帝王时炮塔科技可以立刻点；铁匠铺/大学木材 -100 也压低升级支出</t>
+          <t>【阶段1·本体强化】官方帮助文本直接写「您城堡中的火绳枪科技提升了火药单位和炮塔对移动中目标的准确度」——全表唯一一条点名炮塔的命中加成，正好补炮塔「打不中快速单位」这个最大短板；科技研究 +25% 还能加速炮塔科技与整条大学升级链</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -4046,25 +4046,25 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>长城：炮塔生命 +30%；科技费用 -5/10/15%</t>
+          <t>塔驻扎容量 +5；近射孔、草药免费</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>官方原文唯一把「炮塔」与「瞭望箭塔系」并列写出来的加成，炮塔生命 +30%；科技折价顺带压全表研究成本</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="51" customHeight="1">
+          <t>【阶段1·本体强化】驻军 5→10，被拆时更难清空；近射孔免费消除最小射程，塔贴脸也能打</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>火绳枪：炮塔对移动目标的准确度提高；科技研究速度 +25%（团队）</t>
+          <t>斯万箭塔：防御工事攻击力 +2；建筑修理费用 -25%（团队）</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>官方帮助文本直接写「您城堡中的火绳枪科技提升了火药单位和炮塔对移动中目标的准确度」——全表唯一一条点名炮塔的命中加成，正好补炮塔「打不中快速单位」这个最大短板；科技研究 +25% 还能加速炮塔科技与整条大学升级链</t>
+          <t>【阶段1·本体强化】防御工事含炮塔，但炮塔基数 120，+2 几乎无感；真正的价值是修理费 -25%</t>
         </is>
       </c>
     </row>
@@ -4091,10 +4091,10 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4106,27 +4106,27 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>初始石料 +100；防御工事建造速度 +50%</t>
+          <t>攻城和防御工事升级木材 -75%、研究 +100%；加固堡垒：防御工事每分钟回 500 生命</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>开局石料直接翻倍，且炮塔属防御工事，建造再快 50%——立塔速度和石料两处都省</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
+          <t>【阶段1·本体强化】炮塔的整条升级链（含大学防御工事科技）变便宜、研究快一倍，外加守塔时每分回 500 血</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>建筑的石料费用 -15%</t>
+          <t>箭毒：步弓手与防御工事可造成中毒伤害；塔楼和城堡提供的人口空间 +10（团队）</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>炮塔石料 125 → 约 106，且同时压城堡、TC、城墙的石料，长局累积最明显</t>
+          <t>【阶段1·本体强化】防御工事含炮塔，但中毒是否作用于炮弹未验证；人口 +10 是确定的实用项</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -4166,27 +4166,27 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>攻城和防御工事升级木材 -75%、研究 +100%；加固堡垒：防御工事每分钟回 500 生命</t>
+          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）；石矿工速度 +20%</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>炮塔的整条升级链（含大学防御工事科技）变便宜、研究快一倍，外加守塔时每分回 500 血</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+          <t>【阶段2·减费用】白拿炮塔科技（800食/400木）与塔升级链，石料供给也一并解决——但「含炮塔升级」是原文括号的读法，需实测确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -4196,25 +4196,25 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>建筑工速度 +30%；铁匠铺升级不耗金</t>
+          <t>城堡时代可用化学/火枪手；采矿场科技免费；铁匠铺/大学木材费用-100</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>炮塔的攻击与射程升级在铁匠铺，免金等于白拿；建筑工 +30% 让立塔更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
+          <t>【阶段2·减费用】比所有人早一个时代拿到「化学」这个唯一前置，到帝王时炮塔科技可以立刻点；铁匠铺/大学木材 -100 也压低升级支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4226,12 +4226,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>村民收集/建造/修理速度 +5%</t>
+          <t>建筑的石料费用 -15%</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>建造与修理同吃，长期守塔最省农民</t>
+          <t>【阶段2·减费用】炮塔石料 125 → 约 106，且同时压城堡、TC、城墙的石料，长局累积最明显</t>
         </is>
       </c>
     </row>
@@ -4241,10 +4241,10 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>石矿工产石料 + 黄金</t>
+          <t>TC 石料费用 -50%；城堡时代可建营垒</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>石料是第一瓶颈，这条直接把石料转化成黄金，长局石料不断档</t>
+          <t>【阶段2·减费用】石料折扣作用在 TC 与营垒，不是炮塔本体</t>
         </is>
       </c>
     </row>
@@ -4271,10 +4271,10 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>塔驻扎容量 +5；近射孔、草药免费</t>
+          <t>城墙费用 -50%（团队）</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>驻军 5→10，被拆时更难清空；近射孔免费消除最小射程，塔贴脸也能打</t>
+          <t>【阶段2·减费用】炮塔要站在墙上才安全，墙体便宜一半等于塔阵整体变便宜</t>
         </is>
       </c>
     </row>
@@ -4301,10 +4301,10 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4316,25 +4316,25 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>斯万箭塔：防御工事攻击力 +2；建筑修理费用 -25%（团队）</t>
+          <t>建筑工速度 +30%；铁匠铺升级不耗金</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>防御工事含炮塔，但炮塔基数 120，+2 几乎无感；真正的价值是修理费 -25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
+          <t>【阶段2·减费用】炮塔的攻击与射程升级在铁匠铺，免金等于白拿；建筑工 +30% 让立塔更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4346,12 +4346,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>城墙费用 -50%（团队）</t>
+          <t>初始石料 +100；防御工事建造速度 +50%</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>炮塔要站在墙上才安全，墙体便宜一半等于塔阵整体变便宜</t>
+          <t>【阶段2·减费用】开局石料直接翻倍，且炮塔属防御工事，建造再快 50%——立塔速度和石料两处都省</t>
         </is>
       </c>
     </row>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>箭毒：步弓手与防御工事可造成中毒伤害；塔楼和城堡提供的人口空间 +10（团队）</t>
+          <t>石矿工产石料 + 黄金</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>防御工事含炮塔，但中毒是否作用于炮弹未验证；人口 +10 是确定的实用项</t>
+          <t>【阶段3·资源效率】石料是第一瓶颈，这条直接把石料转化成黄金，长局石料不断档</t>
         </is>
       </c>
     </row>
@@ -4391,12 +4391,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>TC 石料费用 -50%；城堡时代可建营垒</t>
+          <t>村民收集/建造/修理速度 +5%</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>石料折扣作用在 TC 与营垒，不是炮塔本体</t>
+          <t>【阶段3·资源效率】建造与修理同吃，长期守塔最省农民</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
           <t>埃塞俄比亚</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>哨站不等于炮塔，只是免费视野与省石料，属间接</t>
+          <t>【阶段3·资源效率】哨站不等于炮塔，只是免费视野与省石料，属间接</t>
         </is>
       </c>
     </row>
@@ -4454,9 +4454,9 @@
           <t>柏柏尔</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>作用在城堡，不是炮塔</t>
+          <t>【阶段4·其他相关】作用在城堡，不是炮塔</t>
         </is>
       </c>
     </row>
@@ -4484,9 +4484,9 @@
           <t>波斯</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>「堡垒」是城堡科技，作用对象是城堡</t>
+          <t>【阶段4·其他相关】「堡垒」是城堡科技，作用对象是城堡</t>
         </is>
       </c>
     </row>
@@ -4514,9 +4514,9 @@
           <t>不列颠</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>写的是「瞭望箭塔系」，与炮塔是两个不同单位线</t>
+          <t>【阶段4·其他相关】写的是「瞭望箭塔系」，与炮塔是两个不同单位线</t>
         </is>
       </c>
     </row>
@@ -4544,9 +4544,9 @@
           <t>凯尔特</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>「箭塔」是弓箭塔，炮塔不吃</t>
+          <t>【阶段4·其他相关】「箭塔」是弓箭塔，炮塔不吃</t>
         </is>
       </c>
     </row>
@@ -4574,9 +4574,9 @@
           <t>马里</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>作用对象是城镇中心</t>
+          <t>【阶段4·其他相关】作用对象是城镇中心</t>
         </is>
       </c>
     </row>
@@ -4604,9 +4604,9 @@
           <t>日本</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>炮塔发射的是炮弹，没有「箭矢」可加</t>
+          <t>【阶段4·其他相关】炮塔发射的是炮弹，没有「箭矢」可加</t>
         </is>
       </c>
     </row>
@@ -4634,9 +4634,9 @@
           <t>斯拉夫</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>官方原文写的是「瞭望塔系」，不含炮塔</t>
+          <t>【阶段4·其他相关】官方原文写的是「瞭望塔系」，不含炮塔</t>
         </is>
       </c>
     </row>
@@ -4664,9 +4664,9 @@
           <t>马其顿人</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>作用对象是哨站</t>
+          <t>【阶段4·其他相关】作用对象是哨站</t>
         </is>
       </c>
     </row>
@@ -4694,9 +4694,9 @@
           <t>普鲁人</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>「堡垒」是古典模式的 Fort 建筑，与炮塔无关</t>
+          <t>【阶段4·其他相关】「堡垒」是古典模式的 Fort 建筑，与炮塔无关</t>
         </is>
       </c>
     </row>
@@ -4724,9 +4724,9 @@
           <t>色雷斯人</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>是经济光环与存放点，不加炮塔战力</t>
+          <t>【阶段4·其他相关】是经济光环与存放点，不加炮塔战力</t>
         </is>
       </c>
     </row>
@@ -4754,9 +4754,9 @@
           <t>斯巴达</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>「堡垒」是古典模式建筑，仅产金</t>
+          <t>【阶段4·其他相关】「堡垒」是古典模式建筑，仅产金</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6118,12 +6118,12 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>排序口径</t>
+          <t>排序口径（四阶段）</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>① 只看直接作用于炮塔本体、或其石料/建造/修理/前置的条目；</t>
+          <t>本表按打法口径分四个阶段排序：先加强炮塔本体，再减它的建造成本，最后才补石料效率。</t>
         </is>
       </c>
     </row>
@@ -6131,47 +6131,47 @@
       <c r="A46" s="12" t="inlineStr"/>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>② 泛经济、人口、兵种类一律剔除（放进「与炮塔无关·可跳过」）；</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="19" customHeight="1">
+          <t>① 阶段 1 · 本体强化 = 直接加强炮塔本体的条目（射程 / 生命 / 命中 / 驻扎 / 回血 / 爆炸范围）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1">
       <c r="A47" s="12" t="inlineStr"/>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>③ 同时到达的门槛越低、替代成本越高，名次越靠前。</t>
+          <t>② 阶段 2 · 减费用 = 降低炮塔及同系防御工事的建造 / 升级费用的条目（建筑石料 -N%、TC/城墙石料折扣、升级免费、前置提前）。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" s="12" t="inlineStr"/>
-      <c r="B48" s="12" t="inlineStr"/>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>③ 阶段 3 · 资源效率 = 石料产能与采集 / 建造效率（石矿工、采石、建筑工与村民效率）。</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>未验证项</t>
-        </is>
-      </c>
+      <c r="A49" s="12" t="inlineStr"/>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>1) 高丽「塔升级免费」是否包含炮塔科技——官方原文括号只注明「升级炮塔需要化学」，</t>
+          <t>④ 阶段 4 · 其他相关 = 偏城堡 / 瞭望箭塔系、只作用于 TC 或哨站、明确对炮塔无效的条目（列出来避免误买）。</t>
         </is>
       </c>
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="12" t="inlineStr"/>
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   读起来像是包含但仍需化学，本表按「包含」计，请在游戏内实测确认。</t>
-        </is>
-      </c>
+      <c r="B50" s="12" t="inlineStr"/>
     </row>
     <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="12" t="inlineStr"/>
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>未验证项</t>
+        </is>
+      </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>2) 图皮「防御工事造成中毒伤害」是否作用于炮塔炮弹。</t>
+          <t>1) 高丽「塔升级免费」是否包含炮塔科技——官方原文括号只注明「升级炮塔需要化学」，</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       <c r="A52" s="12" t="inlineStr"/>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>3) 土耳其「火药技术成本 -50%」是否覆盖炮塔科技（按官方分类应为是）。</t>
+          <t xml:space="preserve">   读起来像是包含但仍需化学，本表按「包含」计，请在游戏内实测确认。</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       <c r="A53" s="12" t="inlineStr"/>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>4) 撒克逊「基础箭矢 +100%」在 mod 里对炮塔的最终效果（+5 后实际打出几发）为 dat 语义推断，</t>
+          <t>2) 图皮「防御工事造成中毒伤害」是否作用于炮塔炮弹。</t>
         </is>
       </c>
     </row>
@@ -6195,63 +6195,59 @@
       <c r="A54" s="12" t="inlineStr"/>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   依据是属性 102 的语义 + 引擎保底 1 发规则 + 条顿同类效果的社区实测，尚未实机验证。</t>
+          <t>3) 土耳其「火药技术成本 -50%」是否覆盖炮塔科技（按官方分类应为是）。</t>
         </is>
       </c>
     </row>
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="12" t="inlineStr"/>
-      <c r="B55" s="12" t="inlineStr"/>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>4) 撒克逊「基础箭矢 +100%」在 mod 里对炮塔的最终效果（+5 后实际打出几发）为 dat 语义推断，</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="19" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="A56" s="12" t="inlineStr"/>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   依据是属性 102 的语义 + 引擎保底 1 发规则 + 条顿同类效果的社区实测，尚未实机验证。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="19" customHeight="1">
+      <c r="A57" s="12" t="inlineStr"/>
+      <c r="B57" s="12" t="inlineStr"/>
+    </row>
+    <row r="58" ht="19" customHeight="1">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>《帝国时代2决定版 文明联盟 箭塔流最优研究顺序 By RemonBo.xlsx》（同一目录）。</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="19" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
+    <row r="59" ht="19" customHeight="1">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>重要：别买重复</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>主选文明已经自带的效果，就不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="12" t="inlineStr"/>
-      <c r="B58" s="12" t="inlineStr">
+    <row r="60" ht="19" customHeight="1">
+      <c r="A60" s="12" t="inlineStr"/>
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>例：主选土耳其 → 首位按钮（土耳其·火炮术）本身就重复了，应直接换第 2/3 位的备选。</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="19" customHeight="1">
-      <c r="A59" s="12" t="inlineStr"/>
-      <c r="B59" s="12" t="inlineStr">
-        <is>
-          <t>所以正确顺序是：先定主选文明（见「主选文明推荐」），再按「剩下的缺口」挑 3 个免费位。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="19" customHeight="1">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>数据来源</t>
-        </is>
-      </c>
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
         </is>
       </c>
     </row>
@@ -6259,17 +6255,37 @@
       <c r="A61" s="12" t="inlineStr"/>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+          <t>所以正确顺序是：先定主选文明（见「主选文明推荐」），再按「剩下的缺口」挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
       <c r="A62" s="12" t="inlineStr">
         <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="19" customHeight="1">
+      <c r="A63" s="12" t="inlineStr"/>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="19" customHeight="1">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
           <t>整理</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>By RemonBo；本表由 DSH 生成。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 炮塔流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 炮塔流最优研究顺序 By RemonBo.xlsx
@@ -20,9 +20,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·炮塔本体强化'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·炮塔本体强化'!$A$1:$E$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·炮塔本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与炮塔无关·可跳过'!$A$1:$D$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与炮塔无关·可跳过'!$1:$1</definedName>
@@ -1620,7 +1620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>S</t>
@@ -1719,103 +1719,103 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>建筑黑暗/封建/城堡/帝王生命+10/20/30/40%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>炮塔也是建筑，帝王 +40%（2220 → 约 3108，全表对炮塔血量最大的一笔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>中国</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>长城（城墙/瞭望箭塔系/炮塔生命+30%）</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>官方原文点名炮塔</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="6" ht="66" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>撒克逊人</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>塔/城堡城堡起基础箭+100%</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>dat 实现是对 unit class 52（塔类）通配加值，炮塔 236 的 class 就是 52；mod 把 +1 放大成 +5，越过「保底 1 发」区间，故在 mod 内确实生效</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>女真</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>加固堡垒（防御工事每分钟回500生命）</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>炮塔属防御工事，持续回血</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>炮塔属防御工事；但基数 120，+2 无感</t>
         </is>
       </c>
     </row>
@@ -1827,76 +1827,76 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>炮塔属防御工事；但基数 120，+2 无感</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>条顿</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>塔驻扎容量+5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>炮塔驻扎 5 → 10，塔更耐拆</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>葡萄牙</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>火绳枪（火药单位攻击移动目标准确度更高）</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>官方明写：提升火药单位与炮塔对移动目标的准确度——炮塔唯一的专属命中加成</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>箭毒（步弓手/防御工事造成中毒伤害）</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>防御工事含炮塔，是否作用于炮弹待实测</t>
         </is>
       </c>
     </row>
@@ -1908,27 +1908,54 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>箭毒（步弓手/防御工事造成中毒伤害）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>防御工事含炮塔，是否作用于炮弹待实测</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>条顿</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>近射孔/草药免费</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>近射孔消除防御工事最小射程</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1940,7 +1967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2140,19 +2167,19 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>建筑黑暗/封建/城堡/帝王生命+10/20/30/40%</t>
+          <t>初始石料+100</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2162,7 +2189,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>炮塔也是建筑，帝王 +40%</t>
+          <t>开局就接近一座炮塔的石料</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2201,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>初始石料+100</t>
+          <t>建筑石料-15%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2189,7 +2216,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>开局就接近一座炮塔的石料</t>
+          <t>炮塔 125 石 → 约 106 石</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2228,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>建筑石料-15%</t>
+          <t>攻城/防御工事升级木材-75%，研究+100%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2216,7 +2243,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>炮塔 125 石 → 约 106 石</t>
+          <t>炮塔升级链整体变便宜变快</t>
         </is>
       </c>
     </row>
@@ -2228,12 +2255,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>攻城/防御工事升级木材-75%，研究+100%</t>
+          <t>建筑工速度+30%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2243,7 +2270,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>炮塔升级链整体变便宜变快</t>
+          <t>炮塔立得更快</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2287,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>建筑工速度+30%</t>
+          <t>铁匠铺升级不耗金</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2270,24 +2297,24 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>炮塔立得更快</t>
+          <t>炮塔射程/攻击升级在铁匠铺</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>铁匠铺升级不耗金</t>
+          <t>村民收集/建造/修理速度+5%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2297,7 +2324,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>炮塔射程/攻击升级在铁匠铺</t>
+          <t>建造与修理都在内</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2336,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>村民收集/建造/修理速度+5%</t>
+          <t>石矿工产石料+黄金</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2324,7 +2351,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>建造与修理都在内</t>
+          <t>石料供给</t>
         </is>
       </c>
     </row>
@@ -2336,22 +2363,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>石矿工产石料+黄金</t>
+          <t>建筑修理费用 -25%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>石料供给</t>
+          <t>守塔阶段省钱（团队）</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2390,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>建筑修理费用 -25%</t>
+          <t>修理工的工作速度 +25%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2378,7 +2405,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>守塔阶段省钱（团队）</t>
+          <t>守塔阶段更快补血（团队）</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2417,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>修理工的工作速度 +25%</t>
+          <t>城墙费用 -50%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2405,24 +2432,24 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>守塔阶段更快补血（团队）</t>
+          <t>护塔墙体便宜一半（团队）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>城墙费用 -50%</t>
+          <t>塔楼和城堡提供的人口空间 +10</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2432,7 +2459,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>护塔墙体便宜一半（团队）</t>
+          <t>塔阵省房屋（团队）</t>
         </is>
       </c>
     </row>
@@ -2444,22 +2471,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>塔楼和城堡提供的人口空间 +10</t>
+          <t>农田费用-40%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>塔阵省房屋（团队）</t>
+          <t>纯经济换节奏</t>
         </is>
       </c>
     </row>
@@ -2471,12 +2498,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>农田费用-40%</t>
+          <t>TC石料费用-50%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2486,34 +2513,34 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>纯经济换节奏</t>
+          <t>省的是 TC 不是炮塔</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>TC石料费用-50%</t>
+          <t>哨站视野 +3 且不消耗石料</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>省的是 TC 不是炮塔</t>
+          <t>哨站 ≠ 炮塔（团队）</t>
         </is>
       </c>
     </row>
@@ -2525,54 +2552,27 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>哨站视野 +3 且不消耗石料</t>
+          <t>黑暗可建城楼（替瞭望塔系）</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>哨站 ≠ 炮塔（团队）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>黑暗可建城楼（替瞭望塔系）</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
           <t>城楼属瞭望塔系，非炮塔</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E23"/>
+  <autoFilter ref="A1:E22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
